--- a/sampleprojects/CorporateTax/excel/states/OH_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/OH_corp.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
   <si>
     <t>DT: Determine OH Filing Requirement</t>
   </si>
@@ -78,7 +78,7 @@
     <t>Ohio receipts below $150K exclusion threshold; result.oh_taxable_gross_receipts &lt; result.oh_cat_exclusion_threshold</t>
   </si>
   <si>
-    <t>result.oh_taxable_gross_receipts &lt; result.oh_cat_exclusion_threshold</t>
+    <t>oh_result.taxable_gross_receipts &lt; oh_result.cat_exclusion_threshold</t>
   </si>
   <si>
     <t>ACTIONS: COMMENTS</t>
@@ -90,7 +90,7 @@
     <t>Physical presence but below exclusion threshold - no tax due; Set no CAT due and zero tax</t>
   </si>
   <si>
-    <t>set result.oh_qualifies_for_no_cat = true; set result.oh_cat_tax = 0.0; set apportionment.state_tax = 0.0;</t>
+    <t>set oh_result.qualifies_for_no_cat = true; set oh_result.cat_tax = 0.0; set apportionment.state_tax = 0.0;</t>
   </si>
   <si>
     <t>X</t>
@@ -99,7 +99,7 @@
     <t>Physical nexus established - CAT calculation required; Mark CAT as due and log bright-line presence</t>
   </si>
   <si>
-    <t>set result.oh_qualifies_for_no_cat = false;</t>
+    <t>set oh_result.qualifies_for_no_cat = false;</t>
   </si>
   <si>
     <t>Economic nexus established - CAT calculation required; Mark CAT as due and log economic nexus</t>
@@ -108,7 +108,7 @@
     <t>No nexus - no filing required; Set no CAT due, zero tax, and refund any payments</t>
   </si>
   <si>
-    <t>set result.oh_qualifies_for_no_cat = true; set result.oh_cat_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments;</t>
+    <t>set oh_result.qualifies_for_no_cat = true; set oh_result.cat_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments;</t>
   </si>
   <si>
     <t>DT: Calculate OH Taxable Gross Receipts</t>
@@ -123,25 +123,25 @@
     <t>Has nexus and above exclusion threshold; result.oh_qualifies_for_no_cat == false</t>
   </si>
   <si>
-    <t>result.oh_qualifies_for_no_cat == false</t>
+    <t>oh_result.qualifies_for_no_cat == false</t>
   </si>
   <si>
     <t>Has receipts excluded from CAT calculation</t>
   </si>
   <si>
-    <t>result.oh_cat_excluded_receipts &gt; 0</t>
+    <t>oh_result.cat_excluded_receipts &gt; 0</t>
   </si>
   <si>
     <t>No nexus or below threshold - no calculation needed</t>
   </si>
   <si>
-    <t>set result.oh_taxable_gross_receipts = 0.0;</t>
+    <t>set oh_result.taxable_gross_receipts = 0.0;</t>
   </si>
   <si>
     <t>Calculate gross receipts after exclusions; Apply exclusions to Ohio-sourced receipts</t>
   </si>
   <si>
-    <t>set result.oh_taxable_gross_receipts = the maximum of (result.oh_taxable_gross_receipts - result.oh_cat_excluded_receipts) and (0.0);</t>
+    <t>set oh_result.taxable_gross_receipts = the maximum of (oh_result.taxable_gross_receipts - oh_result.cat_excluded_receipts) and (0.0);</t>
   </si>
   <si>
     <t>Use Ohio-sourced gross receipts (no exclusions); Log CAT basis and situsing</t>
@@ -162,31 +162,31 @@
     <t>Has positive Ohio-sourced gross receipts</t>
   </si>
   <si>
-    <t>result.oh_taxable_gross_receipts &gt; 0</t>
+    <t>oh_result.taxable_gross_receipts &gt; 0</t>
   </si>
   <si>
     <t>Ohio receipts at or above $1M (subject to percentage tax); result.oh_taxable_gross_receipts &gt;= result.oh_cat_minimum_threshold</t>
   </si>
   <si>
-    <t>result.oh_taxable_gross_receipts &gt;= result.oh_cat_minimum_threshold</t>
+    <t>oh_result.taxable_gross_receipts &gt;= oh_result.cat_minimum_threshold</t>
   </si>
   <si>
     <t>No nexus or below exclusion threshold - no CAT</t>
   </si>
   <si>
-    <t>set result.oh_cat_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments;</t>
+    <t>set oh_result.cat_tax = 0.0; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments;</t>
   </si>
   <si>
     <t>Receipts over $1M - calculate percentage tax + minimum; CAT = $150 + (Receipts - $1M) × 0.26%</t>
   </si>
   <si>
-    <t>set result.oh_cat_tax = (result.oh_taxable_gross_receipts - result.oh_cat_minimum_threshold) * result.oh_cat_rate + result.oh_cat_minimum_tax; set apportionment.state_tax = result.oh_cat_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
+    <t>set oh_result.cat_tax = (oh_result.taxable_gross_receipts - oh_result.cat_minimum_threshold) * oh_result.cat_rate + oh_result.cat_minimum_tax; set apportionment.state_tax = oh_result.cat_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
   </si>
   <si>
     <t>Receipts between $150K and $1M - minimum tax only</t>
   </si>
   <si>
-    <t>set result.oh_cat_tax = result.oh_cat_minimum_tax; set apportionment.state_tax = result.oh_cat_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
+    <t>set oh_result.cat_tax = oh_result.cat_minimum_tax; set apportionment.state_tax = oh_result.cat_tax; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
   </si>
   <si>
     <t>No taxable receipts - no CAT</t>
@@ -264,10 +264,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(8 attributes)</t>
+    <t>oh_apportionment</t>
+  </si>
+  <si>
+    <t>(4 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -297,36 +297,12 @@
     <t>Ohio CAT economic nexus: $500,000 in Ohio-sourced gross receipts</t>
   </si>
   <si>
-    <t>state_additions</t>
+    <t>state_tax_rate</t>
   </si>
   <si>
     <t>0.0</t>
   </si>
   <si>
-    <t>Not applicable - Ohio has no income tax</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>OH</t>
-  </si>
-  <si>
-    <t>Ohio state code</t>
-  </si>
-  <si>
-    <t>state_credits</t>
-  </si>
-  <si>
-    <t>Ohio CAT has no credits (tax is based on gross receipts only)</t>
-  </si>
-  <si>
-    <t>state_subtractions</t>
-  </si>
-  <si>
-    <t>state_tax_rate</t>
-  </si>
-  <si>
     <t>Ohio has NO corporate income tax (CAT is calculated separately)</t>
   </si>
   <si>
@@ -342,13 +318,13 @@
     <t>Ohio does not use transaction count threshold</t>
   </si>
   <si>
-    <t>result</t>
+    <t>oh_result</t>
   </si>
   <si>
     <t>(10 attributes)</t>
   </si>
   <si>
-    <t>oh_annual_filing_threshold</t>
+    <t>annual_filing_threshold</t>
   </si>
   <si>
     <t>150000.0</t>
@@ -357,19 +333,19 @@
     <t>Ohio CAT annual filing threshold ($150K - no filing required below this)</t>
   </si>
   <si>
-    <t>oh_cat_excluded_receipts</t>
+    <t>cat_excluded_receipts</t>
   </si>
   <si>
     <t>Receipts excluded from CAT (certain sales, dividends, interest, etc.)</t>
   </si>
   <si>
-    <t>oh_cat_exclusion_threshold</t>
+    <t>cat_exclusion_threshold</t>
   </si>
   <si>
     <t>Ohio CAT exclusion threshold ($150K - no tax due below this amount)</t>
   </si>
   <si>
-    <t>oh_cat_minimum_tax</t>
+    <t>cat_minimum_tax</t>
   </si>
   <si>
     <t>150.0</t>
@@ -378,7 +354,7 @@
     <t>Ohio CAT minimum tax ($150 for receipts between $150K and $1M)</t>
   </si>
   <si>
-    <t>oh_cat_minimum_threshold</t>
+    <t>cat_minimum_threshold</t>
   </si>
   <si>
     <t>1000000.0</t>
@@ -387,7 +363,7 @@
     <t>Ohio CAT minimum tax threshold ($1M - minimum tax applies $150K-$1M)</t>
   </si>
   <si>
-    <t>oh_cat_rate</t>
+    <t>cat_rate</t>
   </si>
   <si>
     <t>0.0026</t>
@@ -396,13 +372,13 @@
     <t>Ohio CAT rate (0.26% = 0.0026) on receipts over $1M</t>
   </si>
   <si>
-    <t>oh_cat_tax</t>
+    <t>cat_tax</t>
   </si>
   <si>
     <t>Ohio Commercial Activity Tax liability (NOT an income tax)</t>
   </si>
   <si>
-    <t>oh_qualifies_for_no_cat</t>
+    <t>qualifies_for_no_cat</t>
   </si>
   <si>
     <t>boolean</t>
@@ -414,13 +390,13 @@
     <t>Ohio-sourced receipts below $150K exclusion threshold - no CAT due</t>
   </si>
   <si>
-    <t>oh_quarterly_filing_threshold</t>
+    <t>quarterly_filing_threshold</t>
   </si>
   <si>
     <t>Ohio CAT quarterly filing threshold ($1M - quarterly filing required above this)</t>
   </si>
   <si>
-    <t>oh_taxable_gross_receipts</t>
+    <t>taxable_gross_receipts</t>
   </si>
   <si>
     <t>Ohio-sourced taxable gross receipts for CAT calculation</t>
@@ -3843,14 +3819,14 @@
       <c r="B7" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>84</v>
+      <c r="C7" s="11" t="s">
+        <v>96</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>14</v>
@@ -3859,7 +3835,7 @@
         <v>86</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>14</v>
@@ -3878,194 +3854,194 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="H8" s="16" t="s">
+      <c r="A8" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="B8" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="D9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>86</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M9" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7" t="s">
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="F10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>86</v>
       </c>
       <c r="H10" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="8" t="s">
+      <c r="F11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>86</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B12" s="6" t="s">
+      <c r="A12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
+      <c r="C12" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>89</v>
@@ -4074,7 +4050,7 @@
         <v>14</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>14</v>
@@ -4083,7 +4059,7 @@
         <v>86</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>14</v>
@@ -4106,7 +4082,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>89</v>
@@ -4115,7 +4091,7 @@
         <v>14</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>14</v>
@@ -4124,7 +4100,7 @@
         <v>86</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I14" s="8" t="s">
         <v>14</v>
@@ -4147,7 +4123,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>89</v>
@@ -4156,7 +4132,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>14</v>
@@ -4165,7 +4141,7 @@
         <v>86</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>14</v>
@@ -4188,16 +4164,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>89</v>
+        <v>119</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>120</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>14</v>
@@ -4206,7 +4182,7 @@
         <v>86</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>14</v>
@@ -4229,7 +4205,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>89</v>
@@ -4238,7 +4214,7 @@
         <v>14</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>14</v>
@@ -4247,7 +4223,7 @@
         <v>86</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>14</v>
@@ -4270,7 +4246,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>89</v>
@@ -4279,7 +4255,7 @@
         <v>14</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>14</v>
@@ -4288,7 +4264,7 @@
         <v>86</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I18" s="8" t="s">
         <v>14</v>
@@ -4303,170 +4279,6 @@
         <v>14</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M20" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M21" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M22" s="8" t="s">
         <v>14</v>
       </c>
     </row>
